--- a/sources/lee_step5.xlsx
+++ b/sources/lee_step5.xlsx
@@ -727,6 +727,11 @@
           <t>When done with 2+4 against Bryan, he will laugh back at Lee and sometimes gain a little energy back.</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>b066f77f-2cf9-45e9-ae19-41234876127b</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>b066f77f-2cf9-45e9-ae19-41234876127b</t>
@@ -774,6 +779,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>b186cd07-1f81-4494-bf28-78196461652c</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>b186cd07-1f81-4494-bf28-78196461652c</t>
@@ -819,6 +829,11 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>9736f543-5f0b-4d41-9d88-4dba289c8e13</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -7059,6 +7074,11 @@
       <c r="K128" t="inlineStr">
         <is>
           <t>mhmhhLhhhm</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>5508724d-2532-494e-91ba-e198355b8ea4</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">

--- a/sources/lee_step5.xlsx
+++ b/sources/lee_step5.xlsx
@@ -4703,6 +4703,11 @@
           <t>– f+4</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>df+4</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
           <t>– Mid Shredder</t>
@@ -4758,6 +4763,11 @@
       <c r="A81" t="inlineStr">
         <is>
           <t>– d+4</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>db+4</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
